--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.57173079334526</v>
+        <v>1.717906253918605</v>
       </c>
       <c r="D2" t="n">
-        <v>11.21841986409593</v>
+        <v>1.822993227915588</v>
       </c>
       <c r="E2" t="n">
-        <v>4.511574784001272</v>
+        <v>0.7331309024002067</v>
       </c>
       <c r="F2" t="n">
-        <v>7.338308033934991</v>
+        <v>1.192475055514436</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.88571845185939</v>
+        <v>1.768929248427151</v>
       </c>
       <c r="D3" t="n">
-        <v>10.75063299334473</v>
+        <v>1.746977861418519</v>
       </c>
       <c r="E3" t="n">
-        <v>4.511574784001272</v>
+        <v>0.7331309024002067</v>
       </c>
       <c r="F3" t="n">
-        <v>7.338308033934991</v>
+        <v>1.192475055514436</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1.450282598638006</v>
+        <v>0.2356709222786759</v>
       </c>
       <c r="D4" t="n">
-        <v>28.32277185371218</v>
+        <v>4.60245042622823</v>
       </c>
       <c r="E4" t="n">
-        <v>4.511574784001272</v>
+        <v>0.7331309024002067</v>
       </c>
       <c r="F4" t="n">
-        <v>7.338308033934991</v>
+        <v>1.192475055514436</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>1.982010123372181</v>
+        <v>0.3220766450479793</v>
       </c>
       <c r="D5" t="n">
-        <v>12.30915977291936</v>
+        <v>2.000238463099396</v>
       </c>
       <c r="E5" t="n">
-        <v>4.511574784001272</v>
+        <v>0.7331309024002067</v>
       </c>
       <c r="F5" t="n">
-        <v>7.338308033934991</v>
+        <v>1.192475055514436</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
